--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_NoCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_NoCF_Demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4231D5-926B-41FD-8272-D15A641E13A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB2829E-447D-40FA-B2B4-ABD255A6FD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="30">
   <si>
     <t>Result</t>
   </si>
@@ -137,55 +137,6 @@
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-Company Name:,Google,
-First Name:,Sahil,
-Last Name:,Malhotra,
-Routing Number:,****2691,
-Account Number:,****5489,
-Billing Address:,	33 Sonoma Street,
-Manhattan,  New York ,  10008,
-Country:,	UNITED STATES,
-Account Type:,Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Monthly,
-Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6207-402998,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,Sahil,
-Last Name:,Malhotra,
-Routing Number:,****2691,
-Account Number:,****5489,
-Billing Address:,	33 Sonoma Street,
-Manhattan,  New York ,  10008,
-Country:,	UNITED STATES,
-Account Type:,Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Monthly,
-Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6207-402998,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
 First Name:,Sahil,
 Last Name:,Malhotra,
 Routing Number:,****2691,
@@ -201,10 +152,10 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
-    <t>Fri Jul 03 20:28:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:38:04 IST 2026</t>
+    <t>Wed Oct 07 23:16:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:21:15 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -229,15 +180,13 @@
 Payment Plan Type:,	Recurring,_x000D_
 Payment Plan Duration:,	Monthly,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 18:58:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 19:06:35 IST 2026</t>
+4. Payment Plan,Monthly payments of $</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 18:46:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 15:56:15 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -261,12 +210,10 @@
 Payment Plan Type:,	Recurring,_x000D_
 Payment Plan Duration:,	Monthly,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 19:10:02 IST 2026</t>
+4. Payment Plan,Monthly payments of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 15:57:59 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -711,7 +658,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -737,11 +684,11 @@
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -772,7 +719,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -780,7 +727,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -858,7 +805,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -888,7 +835,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -919,7 +866,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -927,7 +874,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1000,7 +947,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1026,11 +973,11 @@
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1038,14 +985,38 @@
       <c r="N2" s="8">
         <v>0</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>30</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6207-402998,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,Sahil,_x000D_
+Last Name:,Malhotra,_x000D_
+Routing Number:,****2691,_x000D_
+Account Number:,****8902,_x000D_
+Billing Address:,	33 Sonoma Street,_x000D_
+Manhattan,  New York ,  10008,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Monthly,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,Monthly payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1118,7 +1089,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1144,11 +1115,11 @@
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1156,14 +1127,39 @@
       <c r="N2" s="8">
         <v>0</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>27</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6207-402998,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,Google,_x000D_
+First Name:,Sahil,_x000D_
+Last Name:,Malhotra,_x000D_
+Routing Number:,****2691,_x000D_
+Account Number:,****8901,_x000D_
+Billing Address:,	33 Sonoma Street,_x000D_
+Manhattan,  New York ,  10008,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Monthly,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,Monthly payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
